--- a/data/import_template.xlsx
+++ b/data/import_template.xlsx
@@ -1,49 +1,168 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://markuciai-my.sharepoint.com/personal/a_kolobuckis_betonocentras_lt/Documents/Documents/KonkurentuZemelapis/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_B3774633B0BC56006450CA0A98743A8759A5F189" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EB1A597-A825-4EB1-BCA2-49C856659D57}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pildymo šablonas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Pildymo šablonas" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pildymo šablonas'!$A$1:$S$2</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+  <si>
+    <t>Įrašo ID</t>
+  </si>
+  <si>
+    <t>Įmonės kodas</t>
+  </si>
+  <si>
+    <t>Įmonės pavadinimas</t>
+  </si>
+  <si>
+    <t>Prekės ženklas</t>
+  </si>
+  <si>
+    <t>Miestas</t>
+  </si>
+  <si>
+    <t>Savivaldybė</t>
+  </si>
+  <si>
+    <t>Adresas</t>
+  </si>
+  <si>
+    <t>Platuma</t>
+  </si>
+  <si>
+    <t>Ilguma</t>
+  </si>
+  <si>
+    <t>Veiklos tipas</t>
+  </si>
+  <si>
+    <t>Veikla</t>
+  </si>
+  <si>
+    <t>Mazgas (gamintojas)</t>
+  </si>
+  <si>
+    <t>Maišyklė</t>
+  </si>
+  <si>
+    <t>Našumas (realus)</t>
+  </si>
+  <si>
+    <t>Silosų skaičius</t>
+  </si>
+  <si>
+    <t>Viešas aprašymas</t>
+  </si>
+  <si>
+    <t>Pagrindinis šaltinis</t>
+  </si>
+  <si>
+    <t>Mazgo / gamyklos šaltinis</t>
+  </si>
+  <si>
+    <t>Pastaba</t>
+  </si>
+  <si>
+    <t>pvz-uab-betonas</t>
+  </si>
+  <si>
+    <t>123456789</t>
+  </si>
+  <si>
+    <t>UAB Pavyzdinė įmonė</t>
+  </si>
+  <si>
+    <t>Pavyzdinis betonas</t>
+  </si>
+  <si>
+    <t>Vilnius</t>
+  </si>
+  <si>
+    <t>Vilniaus m. sav.</t>
+  </si>
+  <si>
+    <t>Gamyklos g. 1, Vilnius</t>
+  </si>
+  <si>
+    <t>ready_mix_concrete</t>
+  </si>
+  <si>
+    <t>Betono mišiniai</t>
+  </si>
+  <si>
+    <t>Stetter</t>
+  </si>
+  <si>
+    <t>2x3,35 m³</t>
+  </si>
+  <si>
+    <t>100 m³/val.</t>
+  </si>
+  <si>
+    <t>Trumpas viešai randamas mazgo arba gamyklos aprašymas.</t>
+  </si>
+  <si>
+    <t>https://imones-saltinis.lt/</t>
+  </si>
+  <si>
+    <t>https://mazgo-saltinis.lt/</t>
+  </si>
+  <si>
+    <t>Pastabos, ką dar reikia patikslinti.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F2937"/>
+        <fgColor rgb="FF1F2937"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,130 +175,47 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color rgb="00E5E7EB"/>
+        <color rgb="FFE5E7EB"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImportTemplateTable" displayName="ImportTemplateTable" ref="A1:S2" headerRowCount="1">
-  <autoFilter ref="A1:S2"/>
-  <tableColumns count="19">
-    <tableColumn id="1" name="Įrašo ID"/>
-    <tableColumn id="2" name="Įmonės kodas"/>
-    <tableColumn id="3" name="Įmonės pavadinimas"/>
-    <tableColumn id="4" name="Prekės ženklas"/>
-    <tableColumn id="5" name="Miestas"/>
-    <tableColumn id="6" name="Savivaldybė"/>
-    <tableColumn id="7" name="Adresas"/>
-    <tableColumn id="8" name="Platuma"/>
-    <tableColumn id="9" name="Ilguma"/>
-    <tableColumn id="10" name="Veiklos tipas"/>
-    <tableColumn id="11" name="Veikla"/>
-    <tableColumn id="12" name="Mazgas (gamintojas)"/>
-    <tableColumn id="13" name="Maišyklė"/>
-    <tableColumn id="14" name="Našumas (realus)"/>
-    <tableColumn id="15" name="Silosų skaičius"/>
-    <tableColumn id="16" name="Viešas aprašymas"/>
-    <tableColumn id="17" name="Pagrindinis šaltinis"/>
-    <tableColumn id="18" name="Mazgo / gamyklos šaltinis"/>
-    <tableColumn id="19" name="Pastaba"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -466,228 +502,150 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
-    <col width="42" customWidth="1" min="16" max="16"/>
-    <col width="29" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="38" customWidth="1" min="19" max="19"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
+    <col min="12" max="12" width="21" customWidth="1"/>
+    <col min="13" max="13" width="11" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="17" customWidth="1"/>
+    <col min="16" max="16" width="42" customWidth="1"/>
+    <col min="17" max="17" width="29" customWidth="1"/>
+    <col min="18" max="18" width="28" customWidth="1"/>
+    <col min="19" max="19" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Įrašo ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Įmonės kodas</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Įmonės pavadinimas</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Prekės ženklas</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Miestas</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Savivaldybė</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Adresas</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Platuma</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Ilguma</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Veiklos tipas</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Veikla</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Mazgas (gamintojas)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Maišyklė</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Našumas (realus)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Silosų skaičius</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Viešas aprašymas</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Pagrindinis šaltinis</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Mazgo / gamyklos šaltinis</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Pastaba</t>
-        </is>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>pvz-uab-betonas</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>123456789</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>UAB Pavyzdinė įmonė</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Pavyzdinis betonas</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Vilnius</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Vilniaus m. sav.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Gamyklos g. 1, Vilnius</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>54.6872</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>25.2797</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>ready_mix_concrete</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Betono mišiniai</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Stetter</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>2x3,35 m³</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>100 m³/val.</t>
-        </is>
-      </c>
-      <c r="O2" s="4" t="n">
+    <row r="2" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="3">
+        <v>54.687199999999997</v>
+      </c>
+      <c r="I2" s="3">
+        <v>25.279699999999998</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="4">
         <v>2</v>
       </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Trumpas viešai randamas mazgo arba gamyklos aprašymas.</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>https://imones-saltinis.lt/</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>https://mazgo-saltinis.lt/</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>Pastabos, ką dar reikia patikslinti.</t>
-        </is>
+      <c r="P2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S2"/>
+  <autoFilter ref="A1:S2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/data/import_template.xlsx
+++ b/data/import_template.xlsx
@@ -1,168 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://markuciai-my.sharepoint.com/personal/a_kolobuckis_betonocentras_lt/Documents/Documents/KonkurentuZemelapis/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_B3774633B0BC56006450CA0A98743A8759A5F189" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EB1A597-A825-4EB1-BCA2-49C856659D57}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Pildymo šablonas" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pildymo šablonas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pildymo šablonas'!$A$1:$S$2</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
-  <si>
-    <t>Įrašo ID</t>
-  </si>
-  <si>
-    <t>Įmonės kodas</t>
-  </si>
-  <si>
-    <t>Įmonės pavadinimas</t>
-  </si>
-  <si>
-    <t>Prekės ženklas</t>
-  </si>
-  <si>
-    <t>Miestas</t>
-  </si>
-  <si>
-    <t>Savivaldybė</t>
-  </si>
-  <si>
-    <t>Adresas</t>
-  </si>
-  <si>
-    <t>Platuma</t>
-  </si>
-  <si>
-    <t>Ilguma</t>
-  </si>
-  <si>
-    <t>Veiklos tipas</t>
-  </si>
-  <si>
-    <t>Veikla</t>
-  </si>
-  <si>
-    <t>Mazgas (gamintojas)</t>
-  </si>
-  <si>
-    <t>Maišyklė</t>
-  </si>
-  <si>
-    <t>Našumas (realus)</t>
-  </si>
-  <si>
-    <t>Silosų skaičius</t>
-  </si>
-  <si>
-    <t>Viešas aprašymas</t>
-  </si>
-  <si>
-    <t>Pagrindinis šaltinis</t>
-  </si>
-  <si>
-    <t>Mazgo / gamyklos šaltinis</t>
-  </si>
-  <si>
-    <t>Pastaba</t>
-  </si>
-  <si>
-    <t>pvz-uab-betonas</t>
-  </si>
-  <si>
-    <t>123456789</t>
-  </si>
-  <si>
-    <t>UAB Pavyzdinė įmonė</t>
-  </si>
-  <si>
-    <t>Pavyzdinis betonas</t>
-  </si>
-  <si>
-    <t>Vilnius</t>
-  </si>
-  <si>
-    <t>Vilniaus m. sav.</t>
-  </si>
-  <si>
-    <t>Gamyklos g. 1, Vilnius</t>
-  </si>
-  <si>
-    <t>ready_mix_concrete</t>
-  </si>
-  <si>
-    <t>Betono mišiniai</t>
-  </si>
-  <si>
-    <t>Stetter</t>
-  </si>
-  <si>
-    <t>2x3,35 m³</t>
-  </si>
-  <si>
-    <t>100 m³/val.</t>
-  </si>
-  <si>
-    <t>Trumpas viešai randamas mazgo arba gamyklos aprašymas.</t>
-  </si>
-  <si>
-    <t>https://imones-saltinis.lt/</t>
-  </si>
-  <si>
-    <t>https://mazgo-saltinis.lt/</t>
-  </si>
-  <si>
-    <t>Pastabos, ką dar reikia patikslinti.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F2937"/>
+        <fgColor rgb="001F2937"/>
       </patternFill>
     </fill>
   </fills>
@@ -175,47 +56,130 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
-        <color rgb="FFE5E7EB"/>
+        <color rgb="00E5E7EB"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImportTemplateTable" displayName="ImportTemplateTable" ref="A1:S2" headerRowCount="1">
+  <autoFilter ref="A1:S2"/>
+  <tableColumns count="19">
+    <tableColumn id="1" name="Įrašo ID"/>
+    <tableColumn id="2" name="Įmonės kodas"/>
+    <tableColumn id="3" name="Įmonės pavadinimas"/>
+    <tableColumn id="4" name="Prekės ženklas"/>
+    <tableColumn id="5" name="Miestas"/>
+    <tableColumn id="6" name="Savivaldybė"/>
+    <tableColumn id="7" name="Adresas"/>
+    <tableColumn id="8" name="Platuma"/>
+    <tableColumn id="9" name="Ilguma"/>
+    <tableColumn id="10" name="Veiklos tipas"/>
+    <tableColumn id="11" name="Veikla"/>
+    <tableColumn id="12" name="Mazgas (gamintojas)"/>
+    <tableColumn id="13" name="Maišyklė"/>
+    <tableColumn id="14" name="Našumas (realus)"/>
+    <tableColumn id="15" name="Silosų skaičius"/>
+    <tableColumn id="16" name="Viešas aprašymas"/>
+    <tableColumn id="17" name="Pagrindinis šaltinis"/>
+    <tableColumn id="18" name="Mazgo / gamyklos šaltinis"/>
+    <tableColumn id="19" name="Pastaba"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -502,150 +466,228 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="8" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
-    <col min="11" max="11" width="17" customWidth="1"/>
-    <col min="12" max="12" width="21" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="17" customWidth="1"/>
-    <col min="16" max="16" width="42" customWidth="1"/>
-    <col min="17" max="17" width="29" customWidth="1"/>
-    <col min="18" max="18" width="28" customWidth="1"/>
-    <col min="19" max="19" width="38" customWidth="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="38" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Įrašo ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Įmonės kodas</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Įmonės pavadinimas</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Prekės ženklas</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Miestas</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Savivaldybė</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Adresas</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Platuma</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Ilguma</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Veiklos tipas</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Veikla</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Mazgas (gamintojas)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Maišyklė</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Našumas (realus)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Silosų skaičius</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Viešas aprašymas</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Pagrindinis šaltinis</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Mazgo / gamyklos šaltinis</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Pastaba</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>pvz-uab-betonas</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>UAB Pavyzdinė įmonė</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Pavyzdinis betonas</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Vilnius</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus m. sav.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Gamyklos g. 1, Vilnius</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>54.6872</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>25.2797</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>ready_mix_concrete</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Betono mišiniai</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Stetter</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2x3,35 m³</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>100 m³/val.</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="3">
-        <v>54.687199999999997</v>
-      </c>
-      <c r="I2" s="3">
-        <v>25.279699999999998</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" s="4">
-        <v>2</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>34</v>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Trumpas viešai randamas mazgo arba gamyklos aprašymas.</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>https://imones-saltinis.lt/</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>https://mazgo-saltinis.lt/</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>Pastabos, ką dar reikia patikslinti.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:S2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/data/import_template.xlsx
+++ b/data/import_template.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pildymo šablonas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pildymo šablonas'!$A$1:$S$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pildymo šablonas'!$A$1:$S$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -155,8 +155,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImportTemplateTable" displayName="ImportTemplateTable" ref="A1:S2" headerRowCount="1">
-  <autoFilter ref="A1:S2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImportTemplateTable" displayName="ImportTemplateTable" ref="A1:S6" headerRowCount="1">
+  <autoFilter ref="A1:S6"/>
   <tableColumns count="19">
     <tableColumn id="1" name="Įrašo ID"/>
     <tableColumn id="2" name="Įmonės kodas"/>
@@ -471,28 +471,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
-    <col width="29" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="38" customWidth="1" min="19" max="19"/>
+    <col width="41" customWidth="1" min="17" max="17"/>
+    <col width="41" customWidth="1" min="18" max="18"/>
+    <col width="42" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -683,8 +683,376 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>pvz-betono-centras-vilnius</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>123018186</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>UAB Betono centras</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Betono centras</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Vilnius</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus m. sav.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Naujoji Riovonių g. 11, Vilnius</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>54.6560815</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>25.2314767</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>ready_mix_concrete</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Betono mišiniai</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Stetter</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2x3,35 m³</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>100 m³/val.</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Viešai skelbiamas Betono centro betono mazgas Vilniuje.</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>https://betonocentras.lt/kontaktai/</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>https://betonocentras.lt/kontaktai/</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>Pavyzdinė eilutė iš esamų duomenų; trūkstami techniniai duomenys pažymėti aiškiai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>pvz-betono-centras-klaipeda</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>123018186</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>UAB Betono centras</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Betono centras</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Klaipėda</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Klaipėdos m. sav.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Liepų g. 87N, Klaipėda</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>55.7290357</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>21.1544709</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>ready_mix_concrete</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Betono mišiniai</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Klaipėdos betono mazgas</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Viešai skelbiamas Betono centro betono mazgas Klaipėdoje.</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>https://betonocentras.lt/kontaktai/</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>https://betonocentras.lt/kontaktai/</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>Pavyzdinė eilutė iš esamų duomenų; parodyta, kaip pildyti eilutę, kai dalis techninių duomenų nerasta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>pvz-transdosa-druskininkai</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>UAB Transdosa</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Transdosa</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Druskininkai</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Druskininkų sav.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Žvyro g. 2A, Margų k., Druskininkų sav.</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>54.146785</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>23.9291769</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>ready_mix_concrete</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Betono mišiniai</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Elkomix-90 quick master</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1,5 m³</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>40 m³/h</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Viešai skelbiamas betono mišinių tiekėjas Druskininkų regione.</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.transdosa.lt/kontaktai/</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.transdosa.lt/betonas/</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>Techniniai mazgo duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>pvz-telsiu-keliai-telsiai</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>180200843</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>UAB Telšių keliai</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Telšių keliai</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Telšiai</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Telšių r. sav.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Mažeikių g. 18, Telšiai</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>56.0004158</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>22.2581129</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>ready_mix_concrete</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Betono mišiniai</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Elkon</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Oficialiame įmonės puslapyje skelbiama betono mišinių gamyba ir prekyba.</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>Įtraukta pagal naudotojo informaciją; veikla patvirtinta oficialiame lietuviškame įmonės puslapyje.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S2"/>
+  <autoFilter ref="A1:S6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
